--- a/jpcore-r4/feature/swg2-dental/StructureDefinition-jp-diagnosticreport-dentaloral.xlsx
+++ b/jpcore-r4/feature/swg2-dental/StructureDefinition-jp-diagnosticreport-dentaloral.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2071" uniqueCount="392">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2071" uniqueCount="394">
   <si>
     <t>Property</t>
   </si>
@@ -843,10 +843,16 @@
     <t>DiagnosticReport.category:dentaloral.coding.system</t>
   </si>
   <si>
+    <t>http://loinc.org</t>
+  </si>
+  <si>
     <t>DiagnosticReport.category:dentaloral.coding.version</t>
   </si>
   <si>
     <t>DiagnosticReport.category:dentaloral.coding.code</t>
+  </si>
+  <si>
+    <t>LP31759-1</t>
   </si>
   <si>
     <t>DiagnosticReport.category:dentaloral.coding.display</t>
@@ -5183,7 +5189,7 @@
       </c>
       <c r="Q32" s="2"/>
       <c r="R32" t="s" s="2">
-        <v>81</v>
+        <v>266</v>
       </c>
       <c r="S32" t="s" s="2">
         <v>81</v>
@@ -5254,7 +5260,7 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B33" t="s" s="2">
         <v>219</v>
@@ -5368,7 +5374,7 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B34" t="s" s="2">
         <v>226</v>
@@ -5411,7 +5417,7 @@
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
-        <v>81</v>
+        <v>269</v>
       </c>
       <c r="S34" t="s" s="2">
         <v>81</v>
@@ -5482,7 +5488,7 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="B35" t="s" s="2">
         <v>232</v>
@@ -5596,7 +5602,7 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B36" t="s" s="2">
         <v>238</v>
@@ -5712,7 +5718,7 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B37" t="s" s="2">
         <v>247</v>
@@ -5828,14 +5834,14 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -5857,10 +5863,10 @@
         <v>179</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -5891,7 +5897,7 @@
       </c>
       <c r="Y38" s="2"/>
       <c r="Z38" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>81</v>
@@ -5909,7 +5915,7 @@
         <v>81</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>91</v>
@@ -5924,28 +5930,28 @@
         <v>103</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -5964,19 +5970,19 @@
         <v>92</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>81</v>
@@ -6025,7 +6031,7 @@
         <v>81</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
@@ -6040,28 +6046,28 @@
         <v>103</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -6080,19 +6086,19 @@
         <v>92</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>81</v>
@@ -6141,7 +6147,7 @@
         <v>81</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
@@ -6156,28 +6162,28 @@
         <v>103</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -6196,19 +6202,19 @@
         <v>92</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>81</v>
@@ -6257,7 +6263,7 @@
         <v>81</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
@@ -6272,28 +6278,28 @@
         <v>103</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -6312,19 +6318,19 @@
         <v>92</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>81</v>
@@ -6373,7 +6379,7 @@
         <v>81</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
@@ -6391,25 +6397,25 @@
         <v>81</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -6428,19 +6434,19 @@
         <v>92</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>81</v>
@@ -6489,7 +6495,7 @@
         <v>81</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
@@ -6504,28 +6510,28 @@
         <v>103</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -6544,19 +6550,19 @@
         <v>92</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>81</v>
@@ -6605,7 +6611,7 @@
         <v>81</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
@@ -6620,24 +6626,24 @@
         <v>103</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6660,19 +6666,19 @@
         <v>81</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>81</v>
@@ -6721,7 +6727,7 @@
         <v>81</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
@@ -6739,10 +6745,10 @@
         <v>81</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>81</v>
@@ -6750,14 +6756,14 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -6776,19 +6782,19 @@
         <v>81</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>81</v>
@@ -6837,7 +6843,7 @@
         <v>81</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
@@ -6855,10 +6861,10 @@
         <v>81</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>81</v>
@@ -6866,10 +6872,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6892,16 +6898,16 @@
         <v>81</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -6951,7 +6957,7 @@
         <v>81</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
@@ -6972,7 +6978,7 @@
         <v>81</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>81</v>
@@ -6980,14 +6986,14 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -7006,19 +7012,19 @@
         <v>92</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>81</v>
@@ -7067,7 +7073,7 @@
         <v>81</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
@@ -7085,10 +7091,10 @@
         <v>81</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>81</v>
@@ -7096,10 +7102,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7208,10 +7214,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7322,14 +7328,14 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -7351,10 +7357,10 @@
         <v>137</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="N51" t="s" s="2">
         <v>140</v>
@@ -7409,7 +7415,7 @@
         <v>81</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
@@ -7438,10 +7444,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7467,16 +7473,16 @@
         <v>191</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>81</v>
@@ -7525,7 +7531,7 @@
         <v>81</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
@@ -7546,7 +7552,7 @@
         <v>81</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>81</v>
@@ -7554,10 +7560,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7580,13 +7586,13 @@
         <v>92</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -7637,7 +7643,7 @@
         <v>81</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>91</v>
@@ -7658,7 +7664,7 @@
         <v>81</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>81</v>
@@ -7666,14 +7672,14 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -7695,14 +7701,14 @@
         <v>191</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>81</v>
@@ -7751,7 +7757,7 @@
         <v>81</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
@@ -7769,10 +7775,10 @@
         <v>81</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>81</v>
@@ -7780,10 +7786,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7809,13 +7815,13 @@
         <v>179</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -7844,28 +7850,28 @@
         <v>182</v>
       </c>
       <c r="Y55" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="Z55" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="AA55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF55" t="s" s="2">
         <v>383</v>
-      </c>
-      <c r="Z55" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="AA55" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB55" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC55" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD55" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE55" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF55" t="s" s="2">
-        <v>381</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
@@ -7883,10 +7889,10 @@
         <v>81</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>81</v>
@@ -7894,10 +7900,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7920,19 +7926,19 @@
         <v>81</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>81</v>
@@ -7981,7 +7987,7 @@
         <v>81</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
@@ -7999,10 +8005,10 @@
         <v>81</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>81</v>

--- a/jpcore-r4/feature/swg2-dental/StructureDefinition-jp-diagnosticreport-dentaloral.xlsx
+++ b/jpcore-r4/feature/swg2-dental/StructureDefinition-jp-diagnosticreport-dentaloral.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2071" uniqueCount="394">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2506" uniqueCount="422">
   <si>
     <t>Property</t>
   </si>
@@ -887,6 +887,91 @@
   </si>
   <si>
     <t>FiveWs.what[x]</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.code.id</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.code.extension</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.code.coding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:coding.system}
+</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.code.coding:dentaloral</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.code.coding:dentaloral.id</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.code.coding.id</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.code.coding:dentaloral.extension</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.code.coding.extension</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.code.coding:dentaloral.system</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.code.coding.system</t>
+  </si>
+  <si>
+    <t>用語システムのアイデンティティ / Identity of the terminology system</t>
+  </si>
+  <si>
+    <t>コード内のシンボルの意味を定義するコードシステムの識別。 / The identification of the code system that defines the meaning of the symbol in the code.</t>
+  </si>
+  <si>
+    <t>http://jpfhir.jp/fhir/core/CodeSystem/JP_DocumentCodes_CS</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.code.coding:dentaloral.version</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.code.coding.version</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.code.coding:dentaloral.code</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.code.coding.code</t>
+  </si>
+  <si>
+    <t>システムによって定義された構文のシンボル / Symbol in syntax defined by the system</t>
+  </si>
+  <si>
+    <t>システムによって定義された構文のシンボル。シンボルは、定義されたコードまたはコーディングシステムによって定義された構文の式（例：調整後）である場合があります。 / A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
+  </si>
+  <si>
+    <t>32453-3</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.code.coding:dentaloral.display</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.code.coding.display</t>
+  </si>
+  <si>
+    <t>システムによって定義された表現 / Representation defined by the system</t>
+  </si>
+  <si>
+    <t>システムのルールに従って、システム内のコードの意味の表現。 / A representation of the meaning of the code in the system, following the rules of the system.</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.code.coding:dentaloral.userSelected</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.code.coding.userSelected</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.code.text</t>
   </si>
   <si>
     <t>DiagnosticReport.subject</t>
@@ -1552,7 +1637,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN56"/>
+  <dimension ref="A1:AN68"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="54.7421875" customWidth="true" bestFit="true"/>
@@ -5951,7 +6036,7 @@
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>282</v>
+        <v>81</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -5967,23 +6052,19 @@
         <v>81</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>283</v>
+        <v>191</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>284</v>
+        <v>192</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>286</v>
-      </c>
+        <v>193</v>
+      </c>
+      <c r="N39" s="2"/>
+      <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>81</v>
       </c>
@@ -6031,7 +6112,7 @@
         <v>81</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>281</v>
+        <v>194</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
@@ -6043,38 +6124,38 @@
         <v>81</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>103</v>
+        <v>81</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>287</v>
+        <v>81</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>288</v>
+        <v>81</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>289</v>
+        <v>195</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>290</v>
+        <v>81</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>291</v>
+        <v>282</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>291</v>
+        <v>282</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>292</v>
+        <v>136</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>81</v>
@@ -6083,23 +6164,21 @@
         <v>81</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>293</v>
+        <v>137</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>294</v>
+        <v>138</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>294</v>
+        <v>197</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="O40" t="s" s="2">
-        <v>296</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>81</v>
       </c>
@@ -6135,62 +6214,62 @@
         <v>81</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>81</v>
+        <v>198</v>
       </c>
       <c r="AC40" t="s" s="2">
-        <v>81</v>
+        <v>199</v>
       </c>
       <c r="AD40" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>81</v>
+        <v>186</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>291</v>
+        <v>200</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>297</v>
+        <v>81</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>298</v>
+        <v>81</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>299</v>
+        <v>195</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>300</v>
+        <v>81</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>301</v>
+        <v>283</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>301</v>
+        <v>283</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>302</v>
+        <v>81</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>81</v>
@@ -6202,19 +6281,19 @@
         <v>92</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>303</v>
+        <v>202</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>304</v>
+        <v>203</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>304</v>
+        <v>204</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>305</v>
+        <v>205</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>306</v>
+        <v>206</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>81</v>
@@ -6251,25 +6330,23 @@
         <v>81</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC41" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>284</v>
+      </c>
+      <c r="AC41" s="2"/>
       <c r="AD41" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>81</v>
+        <v>186</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>301</v>
+        <v>207</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>81</v>
@@ -6278,32 +6355,34 @@
         <v>103</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>307</v>
+        <v>81</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>308</v>
+        <v>208</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>309</v>
+        <v>209</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>310</v>
+        <v>81</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>311</v>
+        <v>285</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>311</v>
-      </c>
-      <c r="C42" s="2"/>
+        <v>283</v>
+      </c>
+      <c r="C42" t="s" s="2">
+        <v>256</v>
+      </c>
       <c r="D42" t="s" s="2">
-        <v>312</v>
+        <v>81</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="G42" t="s" s="2">
         <v>91</v>
@@ -6318,19 +6397,19 @@
         <v>92</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>313</v>
+        <v>202</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>314</v>
+        <v>203</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>314</v>
+        <v>204</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>315</v>
+        <v>205</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>316</v>
+        <v>206</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>81</v>
@@ -6379,13 +6458,13 @@
         <v>81</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>311</v>
+        <v>207</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>81</v>
@@ -6397,32 +6476,32 @@
         <v>81</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>317</v>
+        <v>208</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>318</v>
+        <v>209</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>319</v>
+        <v>81</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>320</v>
+        <v>286</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>320</v>
+        <v>287</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>321</v>
+        <v>81</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>81</v>
@@ -6431,23 +6510,19 @@
         <v>81</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>322</v>
+        <v>191</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>323</v>
+        <v>192</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>323</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>325</v>
-      </c>
+        <v>193</v>
+      </c>
+      <c r="N43" s="2"/>
+      <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>81</v>
       </c>
@@ -6495,43 +6570,43 @@
         <v>81</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>320</v>
+        <v>194</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>103</v>
+        <v>81</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>326</v>
+        <v>81</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>327</v>
+        <v>81</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>328</v>
+        <v>195</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>329</v>
+        <v>81</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>330</v>
+        <v>288</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>330</v>
+        <v>289</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>331</v>
+        <v>136</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -6547,23 +6622,21 @@
         <v>81</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>322</v>
+        <v>137</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>332</v>
+        <v>138</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>332</v>
+        <v>197</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>333</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>325</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>81</v>
       </c>
@@ -6599,19 +6672,19 @@
         <v>81</v>
       </c>
       <c r="AB44" t="s" s="2">
-        <v>81</v>
+        <v>198</v>
       </c>
       <c r="AC44" t="s" s="2">
-        <v>81</v>
+        <v>199</v>
       </c>
       <c r="AD44" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>81</v>
+        <v>186</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>330</v>
+        <v>200</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
@@ -6623,27 +6696,27 @@
         <v>81</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>326</v>
+        <v>81</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>334</v>
+        <v>81</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>328</v>
+        <v>195</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>329</v>
+        <v>81</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>335</v>
+        <v>290</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>335</v>
+        <v>291</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6654,7 +6727,7 @@
         <v>79</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>81</v>
@@ -6663,29 +6736,29 @@
         <v>81</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>336</v>
+        <v>105</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>337</v>
+        <v>292</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>337</v>
+        <v>293</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>338</v>
+        <v>214</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>339</v>
+        <v>215</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>81</v>
       </c>
       <c r="Q45" s="2"/>
       <c r="R45" t="s" s="2">
-        <v>81</v>
+        <v>294</v>
       </c>
       <c r="S45" t="s" s="2">
         <v>81</v>
@@ -6727,13 +6800,13 @@
         <v>81</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>335</v>
+        <v>216</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>81</v>
@@ -6745,10 +6818,10 @@
         <v>81</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>340</v>
+        <v>217</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>289</v>
+        <v>218</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>81</v>
@@ -6756,21 +6829,21 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>341</v>
+        <v>295</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>341</v>
+        <v>296</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>342</v>
+        <v>81</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>81</v>
@@ -6779,23 +6852,21 @@
         <v>81</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>343</v>
+        <v>191</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>344</v>
+        <v>220</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>344</v>
+        <v>221</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>345</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>346</v>
-      </c>
+        <v>222</v>
+      </c>
+      <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>81</v>
       </c>
@@ -6843,13 +6914,13 @@
         <v>81</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>341</v>
+        <v>223</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>81</v>
@@ -6861,10 +6932,10 @@
         <v>81</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>347</v>
+        <v>224</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>348</v>
+        <v>225</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>81</v>
@@ -6872,10 +6943,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>349</v>
+        <v>297</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>349</v>
+        <v>298</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6883,10 +6954,10 @@
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>81</v>
@@ -6895,27 +6966,27 @@
         <v>81</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>350</v>
+        <v>111</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>351</v>
+        <v>299</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>351</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="O47" s="2"/>
+        <v>300</v>
+      </c>
+      <c r="N47" s="2"/>
+      <c r="O47" t="s" s="2">
+        <v>228</v>
+      </c>
       <c r="P47" t="s" s="2">
         <v>81</v>
       </c>
       <c r="Q47" s="2"/>
       <c r="R47" t="s" s="2">
-        <v>81</v>
+        <v>301</v>
       </c>
       <c r="S47" t="s" s="2">
         <v>81</v>
@@ -6957,13 +7028,13 @@
         <v>81</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>349</v>
+        <v>229</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>81</v>
@@ -6975,10 +7046,10 @@
         <v>81</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>81</v>
+        <v>230</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>353</v>
+        <v>231</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>81</v>
@@ -6986,21 +7057,21 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>354</v>
+        <v>302</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>354</v>
+        <v>303</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>355</v>
+        <v>81</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>81</v>
@@ -7012,19 +7083,17 @@
         <v>92</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>356</v>
+        <v>191</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>357</v>
+        <v>304</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>358</v>
-      </c>
+        <v>305</v>
+      </c>
+      <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
-        <v>359</v>
+        <v>234</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>81</v>
@@ -7073,13 +7142,13 @@
         <v>81</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>354</v>
+        <v>235</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>81</v>
@@ -7091,10 +7160,10 @@
         <v>81</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>360</v>
+        <v>236</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>348</v>
+        <v>237</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>81</v>
@@ -7102,10 +7171,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>361</v>
+        <v>306</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>361</v>
+        <v>307</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7125,19 +7194,23 @@
         <v>81</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>191</v>
+        <v>239</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>192</v>
+        <v>240</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="N49" s="2"/>
-      <c r="O49" s="2"/>
+        <v>241</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="O49" t="s" s="2">
+        <v>243</v>
+      </c>
       <c r="P49" t="s" s="2">
         <v>81</v>
       </c>
@@ -7185,7 +7258,7 @@
         <v>81</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>194</v>
+        <v>244</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>79</v>
@@ -7197,16 +7270,16 @@
         <v>81</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>81</v>
+        <v>245</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>195</v>
+        <v>246</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>81</v>
@@ -7214,21 +7287,21 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>362</v>
+        <v>308</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>362</v>
+        <v>308</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>136</v>
+        <v>81</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>81</v>
@@ -7237,21 +7310,23 @@
         <v>81</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>137</v>
+        <v>191</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>138</v>
+        <v>248</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>197</v>
+        <v>249</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O50" s="2"/>
+        <v>250</v>
+      </c>
+      <c r="O50" t="s" s="2">
+        <v>251</v>
+      </c>
       <c r="P50" t="s" s="2">
         <v>81</v>
       </c>
@@ -7299,28 +7374,28 @@
         <v>81</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>200</v>
+        <v>252</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>81</v>
+        <v>253</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>195</v>
+        <v>254</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>81</v>
@@ -7328,45 +7403,45 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>363</v>
+        <v>309</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>363</v>
+        <v>309</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>364</v>
+        <v>310</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I51" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="J51" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>137</v>
+        <v>311</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>365</v>
+        <v>312</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>366</v>
+        <v>312</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>140</v>
+        <v>313</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>146</v>
+        <v>314</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>81</v>
@@ -7415,43 +7490,43 @@
         <v>81</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>367</v>
+        <v>309</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>81</v>
+        <v>315</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>81</v>
+        <v>316</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>134</v>
+        <v>317</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>81</v>
+        <v>318</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>368</v>
+        <v>319</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>368</v>
+        <v>319</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>81</v>
+        <v>320</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -7467,22 +7542,22 @@
         <v>81</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>191</v>
+        <v>321</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>369</v>
+        <v>322</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>370</v>
+        <v>322</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>371</v>
+        <v>323</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>372</v>
+        <v>324</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>81</v>
@@ -7531,7 +7606,7 @@
         <v>81</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>368</v>
+        <v>319</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
@@ -7546,32 +7621,32 @@
         <v>103</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>81</v>
+        <v>325</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>81</v>
+        <v>326</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>373</v>
+        <v>327</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>81</v>
+        <v>328</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>374</v>
+        <v>329</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>374</v>
+        <v>329</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>81</v>
+        <v>330</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="G53" t="s" s="2">
         <v>91</v>
@@ -7586,16 +7661,20 @@
         <v>92</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>375</v>
+        <v>331</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>376</v>
+        <v>332</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>376</v>
-      </c>
-      <c r="N53" s="2"/>
-      <c r="O53" s="2"/>
+        <v>332</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="O53" t="s" s="2">
+        <v>334</v>
+      </c>
       <c r="P53" t="s" s="2">
         <v>81</v>
       </c>
@@ -7643,10 +7722,10 @@
         <v>81</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>374</v>
+        <v>329</v>
       </c>
       <c r="AG53" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="AH53" t="s" s="2">
         <v>91</v>
@@ -7658,28 +7737,28 @@
         <v>103</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>81</v>
+        <v>335</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>81</v>
+        <v>336</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>377</v>
+        <v>337</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>81</v>
+        <v>338</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>378</v>
+        <v>339</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>378</v>
+        <v>339</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>379</v>
+        <v>340</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -7695,20 +7774,22 @@
         <v>81</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>191</v>
+        <v>341</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>337</v>
-      </c>
-      <c r="N54" s="2"/>
+        <v>342</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>343</v>
+      </c>
       <c r="O54" t="s" s="2">
-        <v>380</v>
+        <v>344</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>81</v>
@@ -7757,7 +7838,7 @@
         <v>81</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>378</v>
+        <v>339</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
@@ -7775,25 +7856,25 @@
         <v>81</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>381</v>
+        <v>345</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>382</v>
+        <v>346</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>81</v>
+        <v>347</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>383</v>
+        <v>348</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>383</v>
+        <v>348</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>81</v>
+        <v>349</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -7809,21 +7890,23 @@
         <v>81</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>179</v>
+        <v>350</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>337</v>
+        <v>351</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>337</v>
+        <v>351</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="O55" s="2"/>
+        <v>352</v>
+      </c>
+      <c r="O55" t="s" s="2">
+        <v>353</v>
+      </c>
       <c r="P55" t="s" s="2">
         <v>81</v>
       </c>
@@ -7847,13 +7930,13 @@
         <v>81</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>182</v>
+        <v>81</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>385</v>
+        <v>81</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>386</v>
+        <v>81</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>81</v>
@@ -7871,7 +7954,7 @@
         <v>81</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>383</v>
+        <v>348</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
@@ -7886,28 +7969,28 @@
         <v>103</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>81</v>
+        <v>354</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>381</v>
+        <v>355</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>387</v>
+        <v>356</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>81</v>
+        <v>357</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>388</v>
+        <v>358</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>388</v>
+        <v>358</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>81</v>
+        <v>359</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -7923,22 +8006,22 @@
         <v>81</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>389</v>
+        <v>350</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>390</v>
+        <v>360</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>390</v>
+        <v>360</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>391</v>
+        <v>361</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>392</v>
+        <v>353</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>81</v>
@@ -7987,7 +8070,7 @@
         <v>81</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>388</v>
+        <v>358</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
@@ -8002,15 +8085,1391 @@
         <v>103</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>81</v>
+        <v>354</v>
       </c>
       <c r="AL56" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="AM56" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="AN56" t="s" s="2">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="B57" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="C57" s="2"/>
+      <c r="D57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E57" s="2"/>
+      <c r="F57" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G57" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K57" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="L57" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="M57" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="O57" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="P57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q57" s="2"/>
+      <c r="R57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF57" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="AG57" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH57" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ57" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL57" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="AM57" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="AN57" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="B58" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="C58" s="2"/>
+      <c r="D58" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="E58" s="2"/>
+      <c r="F58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K58" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="L58" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="M58" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="O58" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="P58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q58" s="2"/>
+      <c r="R58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF58" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="AG58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ58" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL58" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="AM58" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="AN58" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="B59" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="C59" s="2"/>
+      <c r="D59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E59" s="2"/>
+      <c r="F59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K59" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="L59" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="M59" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="O59" s="2"/>
+      <c r="P59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q59" s="2"/>
+      <c r="R59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF59" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="AG59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ59" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM59" t="s" s="2">
         <v>381</v>
       </c>
-      <c r="AM56" t="s" s="2">
+      <c r="AN59" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="B60" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="C60" s="2"/>
+      <c r="D60" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="E60" s="2"/>
+      <c r="F60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J60" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="K60" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="L60" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="M60" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="N60" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="O60" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="P60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q60" s="2"/>
+      <c r="R60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF60" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="AG60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ60" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL60" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="AM60" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="AN60" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="B61" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="C61" s="2"/>
+      <c r="D61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E61" s="2"/>
+      <c r="F61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G61" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K61" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="L61" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="M61" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="N61" s="2"/>
+      <c r="O61" s="2"/>
+      <c r="P61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q61" s="2"/>
+      <c r="R61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF61" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="AG61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH61" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AK61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM61" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="AN61" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="B62" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="C62" s="2"/>
+      <c r="D62" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="E62" s="2"/>
+      <c r="F62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K62" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="L62" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="M62" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="O62" s="2"/>
+      <c r="P62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q62" s="2"/>
+      <c r="R62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF62" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="AG62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ62" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="AK62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM62" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="AN62" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="B63" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="C63" s="2"/>
+      <c r="D63" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="E63" s="2"/>
+      <c r="F63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I63" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="J63" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="K63" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="L63" t="s" s="2">
         <v>393</v>
       </c>
-      <c r="AN56" t="s" s="2">
+      <c r="M63" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="O63" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="P63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q63" s="2"/>
+      <c r="R63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF63" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="AG63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ63" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="AK63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM63" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="AN63" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="B64" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="C64" s="2"/>
+      <c r="D64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E64" s="2"/>
+      <c r="F64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G64" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K64" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="L64" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="M64" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="N64" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="O64" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="P64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q64" s="2"/>
+      <c r="R64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF64" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="AG64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH64" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ64" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM64" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="AN64" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="B65" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="C65" s="2"/>
+      <c r="D65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E65" s="2"/>
+      <c r="F65" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="G65" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J65" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="K65" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="L65" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="M65" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="N65" s="2"/>
+      <c r="O65" s="2"/>
+      <c r="P65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q65" s="2"/>
+      <c r="R65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF65" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="AG65" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AH65" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ65" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM65" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="AN65" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="B66" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="C66" s="2"/>
+      <c r="D66" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="E66" s="2"/>
+      <c r="F66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G66" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K66" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="L66" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="M66" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="N66" s="2"/>
+      <c r="O66" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="P66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q66" s="2"/>
+      <c r="R66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF66" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="AG66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH66" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ66" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL66" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="AM66" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="AN66" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="B67" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="C67" s="2"/>
+      <c r="D67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E67" s="2"/>
+      <c r="F67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K67" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="L67" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="M67" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="N67" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="O67" s="2"/>
+      <c r="P67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q67" s="2"/>
+      <c r="R67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X67" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="Y67" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="Z67" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="AA67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF67" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="AG67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ67" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL67" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="AM67" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="AN67" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="B68" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="C68" s="2"/>
+      <c r="D68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E68" s="2"/>
+      <c r="F68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K68" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="L68" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="M68" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="O68" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="P68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q68" s="2"/>
+      <c r="R68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF68" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="AG68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ68" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL68" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="AM68" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="AN68" t="s" s="2">
         <v>81</v>
       </c>
     </row>
